--- a/NECP Scenario/Results/Regional Results/EL51_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL51_Capacity.xlsx
@@ -507,25 +507,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.176539052374777E-11</v>
+        <v>1.737115644430042E-11</v>
       </c>
       <c r="C2">
-        <v>6.1609070447247E-12</v>
+        <v>9.096360940421896E-12</v>
       </c>
       <c r="D2">
-        <v>9.052354746435631E-12</v>
+        <v>1.336547307396313E-11</v>
       </c>
       <c r="E2">
-        <v>1.33010021562793E-11</v>
+        <v>1.963843652999175E-11</v>
       </c>
       <c r="F2">
-        <v>1.954359641900172E-11</v>
+        <v>2.885537401552181E-11</v>
       </c>
       <c r="G2">
-        <v>2.871584868006219E-11</v>
+        <v>4.239786164818987E-11</v>
       </c>
       <c r="H2">
-        <v>1.74039154056664E-10</v>
+        <v>2.569624301040891E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.470237406756449E-08</v>
+        <v>3.651125563139453E-08</v>
       </c>
       <c r="C3">
-        <v>2.476767895045575E-08</v>
+        <v>3.66085189478637E-08</v>
       </c>
       <c r="D3">
-        <v>5.140123272808226E-08</v>
+        <v>7.534177636402012E-08</v>
       </c>
       <c r="E3">
-        <v>1.252301750530275E-07</v>
+        <v>1.84874959521339E-07</v>
       </c>
       <c r="F3">
-        <v>4.331145581046812E-07</v>
+        <v>5.932121754707276E-07</v>
       </c>
       <c r="G3">
-        <v>2.221565636609031E-06</v>
+        <v>1.930977151874773E-06</v>
       </c>
       <c r="H3">
-        <v>0.1052356734941698</v>
+        <v>0.2617646000885882</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,22 +562,22 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0331071850999069</v>
+        <v>0.06498503993595819</v>
       </c>
       <c r="D4">
-        <v>0.0331071851174044</v>
+        <v>0.06498503996643019</v>
       </c>
       <c r="E4">
-        <v>0.0771372256352634</v>
+        <v>0.0771673149343286</v>
       </c>
       <c r="F4">
-        <v>0.0863822474111582</v>
+        <v>0.08685688209500041</v>
       </c>
       <c r="G4">
-        <v>0.0957112169297101</v>
+        <v>0.0966886412177361</v>
       </c>
       <c r="H4">
-        <v>0.1047550695416372</v>
+        <v>0.1055267748951391</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,22 +692,22 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1.435305299315743E-08</v>
+        <v>2.11993794436978E-08</v>
       </c>
       <c r="D9">
-        <v>1.666421622747892E-08</v>
+        <v>2.563829455559449E-08</v>
       </c>
       <c r="E9">
-        <v>2.643979003802916E-08</v>
+        <v>3.993741535972563E-08</v>
       </c>
       <c r="F9">
-        <v>2.645880706109443E-08</v>
+        <v>3.996412880998379E-08</v>
       </c>
       <c r="G9">
-        <v>2.648691047114351E-08</v>
+        <v>4.000605979294847E-08</v>
       </c>
       <c r="H9">
-        <v>1.140753499401299E-07</v>
+        <v>1.717769881224709E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.289077016004831</v>
+        <v>1.289077016004972</v>
       </c>
       <c r="C13">
-        <v>1.289077016006554</v>
+        <v>1.289077016007516</v>
       </c>
       <c r="D13">
-        <v>1.289077016010501</v>
+        <v>1.289077016012603</v>
       </c>
       <c r="E13">
-        <v>1.289077016018892</v>
+        <v>1.289077016023258</v>
       </c>
       <c r="F13">
-        <v>1.289077016032564</v>
+        <v>1.289077016040529</v>
       </c>
       <c r="G13">
-        <v>1.289077016059217</v>
+        <v>1.289077016075473</v>
       </c>
       <c r="H13">
-        <v>1.289077016349093</v>
+        <v>1.289077016409296</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -923,25 +923,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.769415852685805E-08</v>
+        <v>2.611299587328245E-08</v>
       </c>
       <c r="C18">
-        <v>1.770443564790335E-08</v>
+        <v>2.61283301811564E-08</v>
       </c>
       <c r="D18">
-        <v>2.989194602944468E-08</v>
+        <v>4.439383996512704E-08</v>
       </c>
       <c r="E18">
-        <v>8.38099574971295E-08</v>
+        <v>1.156946359829545E-07</v>
       </c>
       <c r="F18">
-        <v>2.007101736776404E-07</v>
+        <v>2.747685283063873E-07</v>
       </c>
       <c r="G18">
-        <v>3.231938457874416E-07</v>
+        <v>4.536507334245656E-07</v>
       </c>
       <c r="H18">
-        <v>1.353891573634584E-06</v>
+        <v>2.120856868343044E-06</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -952,22 +952,22 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>9.662535963728853E-09</v>
+        <v>1.434496073900484E-08</v>
       </c>
       <c r="D19">
-        <v>1.394857254723464E-08</v>
+        <v>2.154032475296348E-08</v>
       </c>
       <c r="E19">
-        <v>1.040088653631778E-07</v>
+        <v>2.239496990769541E-07</v>
       </c>
       <c r="F19">
-        <v>0.0707254109151277</v>
+        <v>0.0707254110930832</v>
       </c>
       <c r="G19">
-        <v>0.07072541154348259</v>
+        <v>0.07072541166755369</v>
       </c>
       <c r="H19">
-        <v>0.0707254118130777</v>
+        <v>0.07072541185613269</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1027,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.402890669287051E-08</v>
+        <v>3.549279982892443E-08</v>
       </c>
       <c r="C22">
-        <v>2.40569400772404E-08</v>
+        <v>3.55341801637856E-08</v>
       </c>
       <c r="D22">
-        <v>2.693154596853989E-08</v>
+        <v>3.987180253333053E-08</v>
       </c>
       <c r="E22">
-        <v>4.102075066835875E-08</v>
+        <v>6.083540951189548E-08</v>
       </c>
       <c r="F22">
-        <v>5.787460094397806E-08</v>
+        <v>8.545432307607102E-08</v>
       </c>
       <c r="G22">
-        <v>8.291564563968682E-08</v>
+        <v>1.230879489699683E-07</v>
       </c>
       <c r="H22">
-        <v>5.065953686840948E-07</v>
+        <v>7.518686558558203E-07</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>5.543215357012889E-09</v>
+        <v>8.156257455618473E-09</v>
       </c>
       <c r="D24">
-        <v>2.148795744711819E-08</v>
+        <v>3.212882023538385E-08</v>
       </c>
       <c r="E24">
-        <v>2.385480860165646E-07</v>
+        <v>3.606979409921646E-07</v>
       </c>
       <c r="F24">
-        <v>0.5148596867287826</v>
+        <v>0.565400735495979</v>
       </c>
       <c r="G24">
-        <v>1.087268519306</v>
+        <v>0.9399253458273762</v>
       </c>
       <c r="H24">
-        <v>2.384404209388905</v>
+        <v>2.446305028116884</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1160,22 +1160,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.3547275305860681</v>
+        <v>0.3105628420890528</v>
       </c>
       <c r="D27">
-        <v>0.4982011132864749</v>
+        <v>0.4067092664957228</v>
       </c>
       <c r="E27">
-        <v>0.4982011133964452</v>
+        <v>0.4067092666360017</v>
       </c>
       <c r="F27">
-        <v>0.7371897439448625</v>
+        <v>0.7085355075037929</v>
       </c>
       <c r="G27">
-        <v>1.247064834831487</v>
+        <v>1.024301027116158</v>
       </c>
       <c r="H27">
-        <v>2.11862128632019</v>
+        <v>2.167218036597197</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1212,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>7.539016019807572E-09</v>
+        <v>1.116686920315215E-08</v>
       </c>
       <c r="D29">
-        <v>2.552968132626526E-08</v>
+        <v>4.019912624189455E-08</v>
       </c>
       <c r="E29">
-        <v>1.70984405189413E-07</v>
+        <v>5.944162046400587E-07</v>
       </c>
       <c r="F29">
-        <v>0.0094865635047669</v>
+        <v>0.5071447137657065</v>
       </c>
       <c r="G29">
-        <v>0.7061829262205602</v>
+        <v>0.7061829268041447</v>
       </c>
       <c r="H29">
-        <v>0.706182927437639</v>
+        <v>0.706182927547255</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1264,22 +1264,22 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>5.975967072503224E-09</v>
+        <v>8.820479813680224E-09</v>
       </c>
       <c r="D31">
-        <v>7.774858316956574E-09</v>
+        <v>1.165534926902481E-08</v>
       </c>
       <c r="E31">
-        <v>1.596395287963579E-08</v>
+        <v>2.412059538795938E-08</v>
       </c>
       <c r="F31">
-        <v>2.363248539057651E-08</v>
+        <v>3.514491913917024E-08</v>
       </c>
       <c r="G31">
-        <v>3.178455352542112E-08</v>
+        <v>4.845441312500184E-08</v>
       </c>
       <c r="H31">
-        <v>1.833412150730848E-07</v>
+        <v>2.805451385363889E-07</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1316,22 +1316,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>8.737411676589003E-08</v>
+        <v>1.26775991021151E-07</v>
       </c>
       <c r="D33">
-        <v>8.762084892642483E-08</v>
+        <v>1.27292607462149E-07</v>
       </c>
       <c r="E33">
-        <v>1.090795546099452E-05</v>
+        <v>8.204857079314165E-06</v>
       </c>
       <c r="F33">
-        <v>1.090809552904117E-05</v>
+        <v>8.205038109186647E-06</v>
       </c>
       <c r="G33">
-        <v>1.090821622697235E-05</v>
+        <v>8.205187584245055E-06</v>
       </c>
       <c r="H33">
-        <v>1.090917192629169E-05</v>
+        <v>8.206252492907036E-06</v>
       </c>
     </row>
     <row r="34" spans="1:8">
